--- a/artfynd/A 23762-2025 artfynd.xlsx
+++ b/artfynd/A 23762-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117125502</v>
+        <v>117125501</v>
       </c>
       <c r="B2" t="n">
-        <v>79398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>392</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605970</v>
+        <v>605621</v>
       </c>
       <c r="R2" t="n">
-        <v>6958507</v>
+        <v>6958203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117125507</v>
+        <v>117125502</v>
       </c>
       <c r="B3" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606148</v>
+        <v>605970</v>
       </c>
       <c r="R3" t="n">
-        <v>6958309</v>
+        <v>6958507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117125495</v>
+        <v>117125504</v>
       </c>
       <c r="B4" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605830</v>
+        <v>605975</v>
       </c>
       <c r="R4" t="n">
-        <v>6958359</v>
+        <v>6958487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117125504</v>
+        <v>117125498</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605975</v>
+        <v>605656</v>
       </c>
       <c r="R5" t="n">
-        <v>6958487</v>
+        <v>6958039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117125500</v>
+        <v>117125505</v>
       </c>
       <c r="B6" t="n">
-        <v>79429</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605632</v>
+        <v>606115</v>
       </c>
       <c r="R6" t="n">
-        <v>6958123</v>
+        <v>6958303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117125497</v>
+        <v>117125503</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605683</v>
+        <v>605972</v>
       </c>
       <c r="R7" t="n">
-        <v>6958063</v>
+        <v>6958525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117125501</v>
+        <v>117125507</v>
       </c>
       <c r="B8" t="n">
-        <v>78478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605621</v>
+        <v>606148</v>
       </c>
       <c r="R8" t="n">
-        <v>6958203</v>
+        <v>6958309</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117125503</v>
+        <v>117125500</v>
       </c>
       <c r="B9" t="n">
-        <v>90905</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605972</v>
+        <v>605632</v>
       </c>
       <c r="R9" t="n">
-        <v>6958525</v>
+        <v>6958123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117125508</v>
+        <v>117125493</v>
       </c>
       <c r="B10" t="n">
-        <v>79554</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606170</v>
+        <v>605723</v>
       </c>
       <c r="R10" t="n">
-        <v>6958316</v>
+        <v>6958062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117125493</v>
+        <v>117125509</v>
       </c>
       <c r="B11" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>605723</v>
+        <v>606170</v>
       </c>
       <c r="R11" t="n">
-        <v>6958062</v>
+        <v>6958316</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117125509</v>
+        <v>117125508</v>
       </c>
       <c r="B12" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,15 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117125498</v>
+        <v>117125496</v>
       </c>
       <c r="B13" t="n">
-        <v>95664</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>990</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605656</v>
+        <v>605650</v>
       </c>
       <c r="R13" t="n">
-        <v>6958039</v>
+        <v>6958151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,7 +1822,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1900,37 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117125496</v>
+        <v>117125497</v>
       </c>
       <c r="B14" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605650</v>
+        <v>605683</v>
       </c>
       <c r="R14" t="n">
-        <v>6958151</v>
+        <v>6958063</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,108 +1934,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>117125505</v>
-      </c>
-      <c r="B15" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bergmyran, Mpd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>606115</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6958303</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23762-2025 artfynd.xlsx
+++ b/artfynd/A 23762-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125498</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125505</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125503</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125507</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125493</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125509</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125496</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,8 +1999,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125497</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>